--- a/019_SYNOPSYS_FLUENTICING/gridConvergence_D01_V1.xlsx
+++ b/019_SYNOPSYS_FLUENTICING/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://synopsys.sharepoint.com/sites/IcingAFT/Shared Documents/IPW/IPW3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{25A563CA-0C07-461E-8221-DA631500EC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0660343-C4E8-48A6-9D34-02A818F26126}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{25A563CA-0C07-461E-8221-DA631500EC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A43D6B42-C722-4E82-88EF-8996C00EB887}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="680" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="680" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,22 @@
     <sheet name="ONERAM6 Icing KS_1mm (O)" sheetId="5" r:id="rId10"/>
     <sheet name="ONERAM6 Icing KS (O)" sheetId="6" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -53,6 +67,15 @@
   </si>
   <si>
     <t>CMY [-]: Pitching Moment coefficient about the moment reference center (MRC)</t>
+  </si>
+  <si>
+    <t>Mass of water impinged [kg]: Impinged water mass (patch or total)</t>
+  </si>
+  <si>
+    <t>Mass of ice accreted [kg]: Accreted Ice mass (patch or total)</t>
+  </si>
+  <si>
+    <t>Mass of water evaporated [kg]: Evaporated water mass (patch or total)</t>
   </si>
   <si>
     <t xml:space="preserve"> IMPORTANT NOTES: </t>
@@ -123,6 +146,79 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> add, change, reorder or remove rows/columns</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>(R)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in the Sheet name refers to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>REQUIRED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> data, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">(O) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">is for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>OPTIONAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> data.</t>
     </r>
   </si>
   <si>
@@ -263,10 +359,16 @@
     <t>CFD --&gt;  ENTIRE configuration</t>
   </si>
   <si>
+    <t>Icing --&gt; Y = 32 to 40 [In] | 0.8128 to 1.016 [m] Patch excluding the trailing edge (TE)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ONERA - M6: </t>
   </si>
   <si>
     <t>Icing --&gt; ENTIRE configuration</t>
+  </si>
+  <si>
+    <t>LEVEL 1</t>
   </si>
   <si>
     <t>Roughness Height [mm] (0 if none i.e. smooth, -1 if variable roughness)</t>
@@ -281,6 +383,15 @@
     <t>CMZ (pitching)</t>
   </si>
   <si>
+    <t>LEVEL 2</t>
+  </si>
+  <si>
+    <t>LEVEL 3</t>
+  </si>
+  <si>
+    <t>LEVEL 4</t>
+  </si>
+  <si>
     <t>Leave cells blank if you do not plan to provide the data</t>
   </si>
   <si>
@@ -288,6 +399,9 @@
   </si>
   <si>
     <t>Note that 1mm is the baseline. Everything else is optional</t>
+  </si>
+  <si>
+    <t>1-Bin</t>
   </si>
   <si>
     <t>3-Bin</t>
@@ -299,9 +413,6 @@
     <t>15-Bin</t>
   </si>
   <si>
-    <t>Bin</t>
-  </si>
-  <si>
     <t>Mass of water impinged [kg]</t>
   </si>
   <si>
@@ -311,98 +422,17 @@
     <t>Mass of water evaporated [kg]</t>
   </si>
   <si>
-    <t>Diameter (μm)</t>
-  </si>
-  <si>
     <t>Combined (Mass Fraction Averaged)</t>
   </si>
   <si>
-    <t>LEVEL 1</t>
+    <t>For each bin, insert the weighted water impingement mass as:
+Mass_of_Water_Impinged_Bin_i × Mass_Fraction_Bin_i</t>
   </si>
   <si>
-    <t>LEVEL 2</t>
+    <t>Bin</t>
   </si>
   <si>
-    <t>LEVEL 3</t>
-  </si>
-  <si>
-    <t>LEVEL 4</t>
-  </si>
-  <si>
-    <t>1-Bin</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">5. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>(R)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> in the Sheet name refers to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>REQUIRED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> data, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t xml:space="preserve">(O) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t xml:space="preserve">is for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>OPTIONAL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t xml:space="preserve"> data.</t>
-    </r>
+    <t>Diameter (μm)</t>
   </si>
   <si>
     <t>7-Bin KS = 0.5mm</t>
@@ -413,22 +443,6 @@
   <si>
     <t>7-Bin KS = Variable</t>
   </si>
-  <si>
-    <t>Mass of water evaporated [kg]: Evaporated water mass (patch or total)</t>
-  </si>
-  <si>
-    <t>Mass of water impinged [kg]: Impinged water mass (patch or total)</t>
-  </si>
-  <si>
-    <t>Mass of ice accreted [kg]: Accreted Ice mass (patch or total)</t>
-  </si>
-  <si>
-    <t>Icing --&gt; Y = 32 to 40 [In] | 0.8128 to 1.016 [m] Patch excluding the trailing edge (TE)</t>
-  </si>
-  <si>
-    <t>For each bin, insert the weighted water impingement mass as:
-Mass_of_Water_Impinged_Bin_i × Mass_Fraction_Bin_i</t>
-  </si>
 </sst>
 </file>
 
@@ -437,7 +451,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -803,29 +817,20 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -857,6 +862,30 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -886,21 +915,6 @@
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,10 +999,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1319,23 +1329,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75">
-      <c r="A2" s="49"/>
+      <c r="A2" s="66"/>
     </row>
     <row r="3" spans="1:1" ht="15.75">
-      <c r="A3" s="49"/>
+      <c r="A3" s="66"/>
     </row>
     <row r="4" spans="1:1" ht="15.75">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="66" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.75">
-      <c r="A5" s="49"/>
+      <c r="A5" s="66"/>
     </row>
     <row r="6" spans="1:1" ht="21">
       <c r="A6" s="3" t="s">
@@ -1359,293 +1369,293 @@
     </row>
     <row r="10" spans="1:1" ht="21">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="21">
       <c r="A11" s="3" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="21">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.75">
-      <c r="A13" s="50" t="s">
-        <v>6</v>
+      <c r="A13" s="67" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.75">
-      <c r="A14" s="50"/>
+      <c r="A14" s="67"/>
     </row>
     <row r="15" spans="1:1" ht="21">
       <c r="A15" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="21">
       <c r="A16" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="21">
       <c r="A17" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="21">
       <c r="A18" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="21">
       <c r="A19" s="3" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75">
-      <c r="A20" s="49" t="s">
-        <v>11</v>
+      <c r="A20" s="66" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75">
-      <c r="A21" s="49"/>
+      <c r="A21" s="66"/>
     </row>
     <row r="22" spans="1:5" ht="21">
       <c r="A22" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="21">
       <c r="A23" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21">
       <c r="A24" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="21">
       <c r="A25" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="21">
       <c r="A26" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="21">
       <c r="A27" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" ht="21">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="21">
       <c r="A29" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="21">
       <c r="A30" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="21">
       <c r="A31" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="15.75">
-      <c r="A32" s="49" t="s">
-        <v>22</v>
+      <c r="A32" s="66" t="s">
+        <v>26</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="15.75">
-      <c r="A33" s="49"/>
+      <c r="A33" s="66"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="21">
       <c r="A34" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" ht="21">
       <c r="A35" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5" ht="21">
       <c r="A36" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" ht="21">
       <c r="A37" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5" ht="21">
       <c r="A38" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5" ht="21">
       <c r="A39" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="21">
       <c r="A40" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" spans="1:5" ht="21">
       <c r="A41" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" spans="1:5" ht="21">
       <c r="A42" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" spans="1:5" ht="21">
       <c r="A43" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="15.75">
-      <c r="A44" s="49" t="s">
-        <v>25</v>
+      <c r="A44" s="66" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75">
-      <c r="A45" s="49"/>
+      <c r="A45" s="66"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="21">
       <c r="A46" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" ht="21">
       <c r="A47" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" ht="21">
       <c r="A48" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:5" ht="21">
       <c r="A49" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:5" ht="21">
       <c r="A50" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:5" ht="21">
       <c r="A51" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:5" ht="21">
       <c r="A52" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:5" ht="21">
       <c r="A53" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E53" s="4"/>
     </row>
     <row r="54" spans="1:5" ht="21">
       <c r="A54" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:5" ht="21">
       <c r="A55" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="15.75">
-      <c r="A56" s="49" t="s">
-        <v>35</v>
+      <c r="A56" s="66" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75">
-      <c r="A57" s="49"/>
+      <c r="A57" s="66"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="21">
       <c r="A58" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E58" s="4"/>
     </row>
     <row r="59" spans="1:5" ht="20.25">
       <c r="A59" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E59" s="4"/>
     </row>
     <row r="60" spans="1:5" ht="21">
       <c r="A60" s="3" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E60" s="4"/>
     </row>
     <row r="61" spans="1:5" ht="21">
       <c r="A61" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E61" s="4"/>
     </row>
     <row r="62" spans="1:5" ht="21">
       <c r="A62" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:5" ht="21">
       <c r="A63" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E63" s="4"/>
     </row>
@@ -1729,17 +1739,17 @@
   <sheetData>
     <row r="1" spans="1:1021" s="32" customFormat="1" ht="26.25">
       <c r="A1" s="42"/>
-      <c r="D1" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
+      <c r="D1" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2751,36 +2761,36 @@
       <c r="AMG1" s="31"/>
     </row>
     <row r="2" spans="1:1021" s="6" customFormat="1" ht="59.1" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="69"/>
+      <c r="A2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="3" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A3" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="66"/>
+      <c r="A3" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="65"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3792,26 +3802,26 @@
       <c r="AMG3" s="31"/>
     </row>
     <row r="4" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A4" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="A4" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -4824,40 +4834,40 @@
     </row>
     <row r="5" spans="1:1021">
       <c r="A5" s="43" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:1021">
@@ -5086,20 +5096,20 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A22" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
+      <c r="A22" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6111,26 +6121,26 @@
       <c r="AMG22" s="31"/>
     </row>
     <row r="23" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A23" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
+      <c r="A23" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -7143,40 +7153,40 @@
     </row>
     <row r="24" spans="1:1021">
       <c r="A24" s="43" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:1021">
@@ -7403,20 +7413,20 @@
       <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A41" s="70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
+      <c r="A41" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
       <c r="M41" s="31"/>
       <c r="N41" s="31"/>
       <c r="O41" s="31"/>
@@ -8428,26 +8438,26 @@
       <c r="AMG41" s="31"/>
     </row>
     <row r="42" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A42" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="59"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
+      <c r="A42" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="58"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -9460,40 +9470,40 @@
     </row>
     <row r="43" spans="1:1021">
       <c r="A43" s="43" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:1021">
@@ -9716,26 +9726,26 @@
     </row>
     <row r="59" spans="1:1021">
       <c r="J59" s="24" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K59" s="25"/>
       <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A60" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="70"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="70"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="70"/>
+      <c r="A60" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="77"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="77"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="77"/>
+      <c r="L60" s="77"/>
       <c r="M60" s="31"/>
       <c r="N60" s="31"/>
       <c r="O60" s="31"/>
@@ -10747,26 +10757,26 @@
       <c r="AMG60" s="31"/>
     </row>
     <row r="61" spans="1:1021" s="32" customFormat="1" ht="26.25">
-      <c r="A61" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="57"/>
+      <c r="A61" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="58"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K61" s="56"/>
+      <c r="L61" s="56"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -11779,40 +11789,40 @@
     </row>
     <row r="62" spans="1:1021">
       <c r="A62" s="43" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:1021">
@@ -12083,91 +12093,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25">
-      <c r="A1" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="A1" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59.1" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="69"/>
+      <c r="A2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="76"/>
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
       <c r="L2" s="41"/>
     </row>
     <row r="3" spans="1:12" ht="26.25">
-      <c r="A3" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
+      <c r="A3" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
     </row>
     <row r="4" spans="1:12" ht="26.25">
-      <c r="A4" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="59"/>
-      <c r="I4" s="60"/>
+      <c r="A4" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -12343,62 +12353,62 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="26.25">
-      <c r="A14" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="66"/>
+      <c r="A14" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:12" ht="26.25">
-      <c r="A15" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="60"/>
+      <c r="A15" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -12574,62 +12584,62 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="26.25">
-      <c r="A25" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
+      <c r="A25" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
     </row>
     <row r="26" spans="1:9" ht="26.25">
-      <c r="A26" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="59"/>
-      <c r="I26" s="60"/>
+      <c r="A26" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="58"/>
+      <c r="I26" s="59"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -12805,62 +12815,62 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="26.25">
-      <c r="A36" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="65"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="66"/>
+      <c r="A36" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:9" ht="26.25">
-      <c r="A37" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="59"/>
-      <c r="I37" s="60"/>
+      <c r="A37" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="58"/>
+      <c r="I37" s="59"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -13072,25 +13082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="26.25">
-      <c r="A1" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
     </row>
     <row r="2" spans="1:1024">
       <c r="A2" s="17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -13098,10 +13108,18 @@
       <c r="R2" s="16"/>
     </row>
     <row r="3" spans="1:1024">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="A3" s="11">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.45512000000000002</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1.1209999999999999E-2</v>
+      </c>
+      <c r="D3" s="11">
+        <v>5.9999999999999995E-4</v>
+      </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -14124,12 +14142,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="26.25">
-      <c r="A4" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
+      <c r="A4" s="68" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -14142,16 +14160,16 @@
     </row>
     <row r="5" spans="1:1024">
       <c r="A5" s="17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -14164,10 +14182,18 @@
       <c r="R5" s="7"/>
     </row>
     <row r="6" spans="1:1024">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="11">
+        <v>0</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.45473000000000002</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1.1209999999999999E-2</v>
+      </c>
+      <c r="D6" s="11">
+        <v>4.8000000000000001E-4</v>
+      </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -15190,12 +15216,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="26.25">
-      <c r="A7" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
+      <c r="A7" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -15208,16 +15234,16 @@
     </row>
     <row r="8" spans="1:1024">
       <c r="A8" s="17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -15230,10 +15256,18 @@
       <c r="R8" s="7"/>
     </row>
     <row r="9" spans="1:1024">
-      <c r="A9" s="11"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
+      <c r="A9" s="11">
+        <v>0</v>
+      </c>
+      <c r="B9" s="37">
+        <v>0.45374999999999999</v>
+      </c>
+      <c r="C9" s="37">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="D9" s="37">
+        <v>4.6000000000000001E-4</v>
+      </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -16256,12 +16290,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="26.25">
-      <c r="A10" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
+      <c r="A10" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -16273,16 +16307,16 @@
     </row>
     <row r="11" spans="1:1024">
       <c r="A11" s="17" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -16293,10 +16327,18 @@
       <c r="R11" s="7"/>
     </row>
     <row r="12" spans="1:1024">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="A12" s="11">
+        <v>0</v>
+      </c>
+      <c r="B12" s="11">
+        <v>0.45596999999999999</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1.174E-2</v>
+      </c>
+      <c r="D12" s="11">
+        <v>-8.0000000000000007E-5</v>
+      </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -17328,12 +17370,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="26.25">
-      <c r="A14" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="A14" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17771,31 +17813,31 @@
   <cols>
     <col min="1" max="1" width="58" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="81" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="53" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="1024" width="11.125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26.25">
-      <c r="A1" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
+      <c r="A1" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>48</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
@@ -17815,13 +17857,13 @@
       <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="77">
+      <c r="B3" s="49">
         <v>0.122</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="51">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="D3" s="77">
+      <c r="D3" s="49">
         <v>-4.7399999999999998E-2</v>
       </c>
       <c r="E3" s="10"/>
@@ -17830,12 +17872,12 @@
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A4" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56"/>
+      <c r="A4" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
@@ -17843,16 +17885,16 @@
     </row>
     <row r="5" spans="1:18" s="9" customFormat="1">
       <c r="A5" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="78" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>48</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
@@ -17863,13 +17905,13 @@
       <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="49">
         <v>0.122</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="51">
         <v>1.9E-2</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="49">
         <v>-4.7500000000000001E-2</v>
       </c>
       <c r="E6" s="10"/>
@@ -17880,12 +17922,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A7" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="56"/>
+      <c r="A7" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -17895,16 +17937,16 @@
     </row>
     <row r="8" spans="1:18" s="9" customFormat="1">
       <c r="A8" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="78" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>48</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -17917,13 +17959,13 @@
       <c r="A9" s="11">
         <v>1</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="49">
         <v>0.122</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="49">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="49">
         <v>-4.7600000000000003E-2</v>
       </c>
       <c r="E9" s="12"/>
@@ -17939,12 +17981,12 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A10" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="56"/>
+      <c r="A10" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="72"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -17954,16 +17996,16 @@
     </row>
     <row r="11" spans="1:18" s="9" customFormat="1">
       <c r="A11" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="78" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>48</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -17976,13 +18018,13 @@
       <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="49">
         <v>0.123</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="49">
         <v>1.95E-2</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="49">
         <v>-4.82E-2</v>
       </c>
       <c r="E12" s="10"/>
@@ -17995,7 +18037,7 @@
     <row r="13" spans="1:18" s="9" customFormat="1">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="80"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -18007,12 +18049,12 @@
       <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A14" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
+      <c r="A14" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18023,12 +18065,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" s="9" customFormat="1" ht="26.25">
-      <c r="A15" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
+      <c r="A15" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18041,7 +18083,7 @@
     <row r="16" spans="1:18" s="9" customFormat="1">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="80"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -18055,7 +18097,7 @@
     <row r="17" spans="1:15" s="9" customFormat="1">
       <c r="A17" s="10"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="80"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -18069,7 +18111,7 @@
     <row r="18" spans="1:15" s="9" customFormat="1">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="80"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -18082,7 +18124,7 @@
     </row>
     <row r="19" spans="1:15" s="9" customFormat="1">
       <c r="B19" s="10"/>
-      <c r="C19" s="80"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -18097,7 +18139,7 @@
       <c r="O19" s="10"/>
     </row>
     <row r="20" spans="1:15" s="9" customFormat="1">
-      <c r="C20" s="81"/>
+      <c r="C20" s="53"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
@@ -18105,7 +18147,7 @@
     <row r="21" spans="1:15" s="9" customFormat="1">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
-      <c r="C21" s="82"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -18121,7 +18163,7 @@
     <row r="22" spans="1:15" s="9" customFormat="1">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
-      <c r="C22" s="80"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -18136,7 +18178,7 @@
     </row>
     <row r="23" spans="1:15" s="9" customFormat="1">
       <c r="A23" s="10"/>
-      <c r="C23" s="81"/>
+      <c r="C23" s="53"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="I23" s="10"/>
@@ -18145,14 +18187,14 @@
     </row>
     <row r="24" spans="1:15" s="9" customFormat="1">
       <c r="A24" s="10"/>
-      <c r="C24" s="81"/>
+      <c r="C24" s="53"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="I24" s="10"/>
     </row>
     <row r="25" spans="1:15" s="9" customFormat="1">
       <c r="A25" s="10"/>
-      <c r="C25" s="81"/>
+      <c r="C25" s="53"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="I25" s="10"/>
@@ -18160,7 +18202,7 @@
     <row r="26" spans="1:15" s="9" customFormat="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
-      <c r="C26" s="80"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -18169,7 +18211,7 @@
     <row r="27" spans="1:15" s="9" customFormat="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="80"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -18178,7 +18220,7 @@
     <row r="28" spans="1:15" s="9" customFormat="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
-      <c r="C28" s="80"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -18187,7 +18229,7 @@
     <row r="29" spans="1:15" s="9" customFormat="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="80"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -18196,7 +18238,7 @@
     <row r="30" spans="1:15" s="9" customFormat="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="80"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -18207,7 +18249,7 @@
     <row r="31" spans="1:15" s="9" customFormat="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="80"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -18218,7 +18260,7 @@
     <row r="32" spans="1:15" s="9" customFormat="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
-      <c r="C32" s="80"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -18229,7 +18271,7 @@
     <row r="33" spans="1:12" s="9" customFormat="1">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
-      <c r="C33" s="80"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -18240,7 +18282,7 @@
     <row r="34" spans="1:12" s="9" customFormat="1">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
-      <c r="C34" s="80"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -18251,7 +18293,7 @@
     <row r="35" spans="1:12" s="9" customFormat="1">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
-      <c r="C35" s="80"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -18262,7 +18304,7 @@
     <row r="36" spans="1:12" s="9" customFormat="1">
       <c r="A36" s="10"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="80"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -18273,7 +18315,7 @@
     <row r="37" spans="1:12" s="9" customFormat="1">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="80"/>
+      <c r="C37" s="52"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -18282,7 +18324,7 @@
       <c r="I37" s="10"/>
     </row>
     <row r="38" spans="1:12" s="9" customFormat="1">
-      <c r="C38" s="81"/>
+      <c r="C38" s="53"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
@@ -18291,7 +18333,7 @@
     <row r="40" spans="1:12" s="9" customFormat="1">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
-      <c r="C40" s="82"/>
+      <c r="C40" s="54"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -18305,7 +18347,7 @@
     <row r="41" spans="1:12" s="9" customFormat="1">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
-      <c r="C41" s="80"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -18318,21 +18360,21 @@
     </row>
     <row r="42" spans="1:12" s="9" customFormat="1">
       <c r="A42" s="10"/>
-      <c r="C42" s="81"/>
+      <c r="C42" s="53"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:12" s="9" customFormat="1">
       <c r="A43" s="10"/>
-      <c r="C43" s="81"/>
+      <c r="C43" s="53"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="I43" s="10"/>
     </row>
     <row r="44" spans="1:12" s="9" customFormat="1">
       <c r="A44" s="10"/>
-      <c r="C44" s="81"/>
+      <c r="C44" s="53"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="I44" s="10"/>
@@ -18340,7 +18382,7 @@
     <row r="45" spans="1:12" s="9" customFormat="1">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="80"/>
+      <c r="C45" s="52"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -18349,7 +18391,7 @@
     <row r="46" spans="1:12" s="9" customFormat="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="80"/>
+      <c r="C46" s="52"/>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -18358,7 +18400,7 @@
     <row r="47" spans="1:12" s="9" customFormat="1">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
-      <c r="C47" s="80"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
@@ -18367,7 +18409,7 @@
     <row r="48" spans="1:12" s="9" customFormat="1">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
-      <c r="C48" s="80"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
@@ -18376,7 +18418,7 @@
     <row r="49" spans="1:12" s="9" customFormat="1">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
-      <c r="C49" s="80"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
@@ -18387,7 +18429,7 @@
     <row r="50" spans="1:12" s="9" customFormat="1">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
-      <c r="C50" s="80"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
@@ -18398,7 +18440,7 @@
     <row r="51" spans="1:12" s="9" customFormat="1">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
-      <c r="C51" s="80"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
@@ -18409,7 +18451,7 @@
     <row r="52" spans="1:12" s="9" customFormat="1">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
-      <c r="C52" s="80"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
@@ -18420,7 +18462,7 @@
     <row r="53" spans="1:12" s="9" customFormat="1">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
-      <c r="C53" s="80"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
@@ -18431,7 +18473,7 @@
     <row r="54" spans="1:12" s="9" customFormat="1">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
-      <c r="C54" s="80"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -18442,7 +18484,7 @@
     <row r="55" spans="1:12" s="9" customFormat="1">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
-      <c r="C55" s="80"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
@@ -18453,7 +18495,7 @@
     <row r="56" spans="1:12" s="9" customFormat="1">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
-      <c r="C56" s="80"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
@@ -18462,7 +18504,7 @@
       <c r="I56" s="10"/>
     </row>
     <row r="57" spans="1:12" s="9" customFormat="1">
-      <c r="C57" s="81"/>
+      <c r="C57" s="53"/>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
@@ -18494,25 +18536,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26.25">
-      <c r="A1" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
+      <c r="A1" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="12"/>
@@ -18553,13 +18595,13 @@
       <c r="A4" s="11">
         <v>0.5</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="49">
         <v>0.124</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="49">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="49">
         <v>-4.8399999999999999E-2</v>
       </c>
       <c r="E4" s="10"/>
@@ -18571,13 +18613,13 @@
       <c r="A5" s="11">
         <v>1.5</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B5" s="49">
         <v>0.121</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="49">
         <v>2.07E-2</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="49">
         <v>-4.6800000000000001E-2</v>
       </c>
       <c r="E5" s="10"/>
@@ -18598,12 +18640,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="26.25">
-      <c r="A7" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="56"/>
+      <c r="A7" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="73"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
@@ -18611,16 +18653,16 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -18645,13 +18687,13 @@
       <c r="A10" s="11">
         <v>0.5</v>
       </c>
-      <c r="B10" s="77">
+      <c r="B10" s="49">
         <v>0.124</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="49">
         <v>1.67E-2</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="49">
         <v>-4.8399999999999999E-2</v>
       </c>
       <c r="E10" s="10"/>
@@ -18665,13 +18707,13 @@
       <c r="A11" s="11">
         <v>1.5</v>
       </c>
-      <c r="B11" s="83">
+      <c r="B11" s="55">
         <v>0.121</v>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="55">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D11" s="83">
+      <c r="D11" s="55">
         <v>-4.6899999999999997E-2</v>
       </c>
       <c r="E11" s="10"/>
@@ -18696,12 +18738,12 @@
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:18" ht="26.25">
-      <c r="A13" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
+      <c r="A13" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18711,16 +18753,16 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -18752,13 +18794,13 @@
       <c r="A16" s="11">
         <v>0.5</v>
       </c>
-      <c r="B16" s="83">
+      <c r="B16" s="55">
         <v>0.124</v>
       </c>
-      <c r="C16" s="83">
+      <c r="C16" s="55">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="55">
         <v>-4.8599999999999997E-2</v>
       </c>
       <c r="M16" s="14"/>
@@ -18769,13 +18811,13 @@
       <c r="A17" s="11">
         <v>1.5</v>
       </c>
-      <c r="B17" s="77">
+      <c r="B17" s="49">
         <v>0.121</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="49">
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="49">
         <v>-4.7E-2</v>
       </c>
       <c r="E17" s="10"/>
@@ -18805,12 +18847,12 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="26.25">
-      <c r="A19" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56"/>
+      <c r="A19" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="73"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -18820,16 +18862,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -18856,13 +18898,13 @@
       <c r="A22" s="11">
         <v>0.5</v>
       </c>
-      <c r="B22" s="77">
+      <c r="B22" s="49">
         <v>0.124</v>
       </c>
-      <c r="C22" s="77">
+      <c r="C22" s="49">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="D22" s="77">
+      <c r="D22" s="49">
         <v>-4.8800000000000003E-2</v>
       </c>
       <c r="E22" s="10"/>
@@ -18876,13 +18918,13 @@
       <c r="A23" s="11">
         <v>1.5</v>
       </c>
-      <c r="B23" s="77">
+      <c r="B23" s="49">
         <v>0.122</v>
       </c>
-      <c r="C23" s="77">
+      <c r="C23" s="49">
         <v>2.0899999999999998E-2</v>
       </c>
-      <c r="D23" s="77">
+      <c r="D23" s="49">
         <v>-4.7800000000000002E-2</v>
       </c>
       <c r="E23" s="10"/>
@@ -18925,12 +18967,12 @@
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="26.25">
-      <c r="A26" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
+      <c r="A26" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -18941,12 +18983,12 @@
       <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="26.25">
-      <c r="A27" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
+      <c r="A27" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -19413,405 +19455,501 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="63"/>
+      <c r="A1" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13" ht="26.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+    </row>
+    <row r="3" spans="1:13" ht="26.25">
+      <c r="A3" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-    </row>
-    <row r="3" spans="1:13" ht="26.25">
-      <c r="A3" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="60"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="58"/>
+      <c r="M3" s="59"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="B5" s="34">
+        <v>0.11093600000000001</v>
+      </c>
+      <c r="C5" s="34">
+        <v>0.106687</v>
+      </c>
+      <c r="D5" s="34">
+        <v>4.24873E-3</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.11475100000000001</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.11089499999999999</v>
+      </c>
+      <c r="G5" s="11">
+        <v>3.8555899999999999E-3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.11919</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.115568</v>
+      </c>
+      <c r="J5" s="11">
+        <v>3.62146E-3</v>
+      </c>
+      <c r="K5" s="25">
+        <v>0.120459</v>
+      </c>
+      <c r="L5" s="25">
+        <v>0.11687400000000001</v>
+      </c>
+      <c r="M5" s="25">
+        <v>3.5852000000000002E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="26.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="65"/>
+    </row>
+    <row r="7" spans="1:13" ht="26.25">
+      <c r="A7" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="66"/>
-    </row>
-    <row r="7" spans="1:13" ht="26.25">
-      <c r="A7" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="58"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="58"/>
+      <c r="M7" s="59"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="B9" s="34">
+        <v>0.11126999999999999</v>
+      </c>
+      <c r="C9" s="34">
+        <v>0.107027</v>
+      </c>
+      <c r="D9" s="34">
+        <v>4.24363E-3</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.117284</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.113478</v>
+      </c>
+      <c r="G9" s="11">
+        <v>3.8056700000000001E-3</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.120779</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.11716699999999999</v>
+      </c>
+      <c r="J9" s="11">
+        <v>3.61226E-3</v>
+      </c>
+      <c r="K9" s="25">
+        <v>0.121075</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0.11748400000000001</v>
+      </c>
+      <c r="M9" s="25">
+        <v>3.5907000000000001E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="26.25">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+    </row>
+    <row r="11" spans="1:13" ht="26.25">
+      <c r="A11" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-    </row>
-    <row r="11" spans="1:13" ht="26.25">
-      <c r="A11" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="59"/>
-      <c r="M11" s="60"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="58"/>
+      <c r="M11" s="59"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="17"/>
       <c r="B12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
+        <v>63</v>
+      </c>
+      <c r="B13" s="34">
+        <v>0.112639</v>
+      </c>
+      <c r="C13" s="34">
+        <v>0.108419</v>
+      </c>
+      <c r="D13" s="34">
+        <v>4.2194800000000003E-3</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.12044199999999999</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0.116687</v>
+      </c>
+      <c r="G13" s="11">
+        <v>3.7547600000000002E-3</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.122152</v>
+      </c>
+      <c r="I13" s="37">
+        <v>0.118561</v>
+      </c>
+      <c r="J13" s="37">
+        <v>3.5906699999999998E-3</v>
+      </c>
+      <c r="K13" s="25">
+        <v>0.12223000000000001</v>
+      </c>
+      <c r="L13" s="38">
+        <v>0.118663</v>
+      </c>
+      <c r="M13" s="38">
+        <v>3.5666399999999998E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="26.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+    </row>
+    <row r="15" spans="1:13" ht="26.25">
+      <c r="A15" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="58"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.25">
-      <c r="A15" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="59"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="59"/>
-      <c r="M15" s="60"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="17"/>
       <c r="B16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
+        <v>63</v>
+      </c>
+      <c r="B17" s="34">
+        <v>0.11311499999999999</v>
+      </c>
+      <c r="C17" s="34">
+        <v>0.108858</v>
+      </c>
+      <c r="D17" s="34">
+        <v>4.2569599999999997E-3</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0.12095499999999999</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0.117135</v>
+      </c>
+      <c r="G17" s="11">
+        <v>3.82E-3</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.12252300000000001</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.11885800000000001</v>
+      </c>
+      <c r="J17" s="11">
+        <v>3.6684E-3</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0.122728</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0.119087</v>
+      </c>
+      <c r="M17" s="11">
+        <v>3.6405600000000002E-3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -19863,74 +20001,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25">
-      <c r="A1" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
+      <c r="A1" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
     </row>
     <row r="2" spans="1:17" ht="59.1" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="69"/>
+      <c r="A2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="3" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+    </row>
+    <row r="4" spans="1:17" s="27" customFormat="1" ht="26.25">
+      <c r="A4" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-    </row>
-    <row r="4" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A4" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
@@ -19938,40 +20076,40 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -20310,86 +20448,86 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A22" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
+      <c r="A22" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
       <c r="M22" s="28"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A23" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
+      <c r="A23" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -20715,82 +20853,82 @@
       <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A41" s="70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
+      <c r="A41" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
       <c r="O41" s="29"/>
       <c r="P41" s="29"/>
       <c r="Q41" s="29"/>
     </row>
     <row r="42" spans="1:17" s="27" customFormat="1" ht="26.25">
-      <c r="A42" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
+      <c r="A42" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -21065,79 +21203,79 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="26.25">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
+      <c r="L60" s="56"/>
+    </row>
+    <row r="61" spans="1:12" s="27" customFormat="1" ht="26.25">
+      <c r="A61" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="57"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="57"/>
-      <c r="E60" s="57"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="57"/>
-      <c r="L60" s="57"/>
-    </row>
-    <row r="61" spans="1:12" s="27" customFormat="1" ht="26.25">
-      <c r="A61" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="57"/>
+      <c r="K61" s="56"/>
+      <c r="L61" s="56"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -21463,405 +21601,501 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="63"/>
+      <c r="A1" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13" ht="26.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+    </row>
+    <row r="3" spans="1:13" ht="26.25">
+      <c r="A3" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-    </row>
-    <row r="3" spans="1:13" ht="26.25">
-      <c r="A3" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="60"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="58"/>
+      <c r="M3" s="59"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="17"/>
       <c r="B4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="B5" s="34">
+        <v>0.10964</v>
+      </c>
+      <c r="C5" s="34">
+        <v>0.101964</v>
+      </c>
+      <c r="D5" s="34">
+        <v>7.6747899999999999E-3</v>
+      </c>
+      <c r="E5" s="34">
+        <v>0.115024</v>
+      </c>
+      <c r="F5" s="34">
+        <v>0.107584</v>
+      </c>
+      <c r="G5" s="34">
+        <v>7.4396200000000001E-3</v>
+      </c>
+      <c r="H5" s="34">
+        <v>0.118973</v>
+      </c>
+      <c r="I5" s="34">
+        <v>0.11192199999999999</v>
+      </c>
+      <c r="J5" s="34">
+        <v>7.0479799999999997E-3</v>
+      </c>
+      <c r="K5" s="34">
+        <v>0.12017</v>
+      </c>
+      <c r="L5" s="34">
+        <v>0.11321299999999999</v>
+      </c>
+      <c r="M5" s="34">
+        <v>6.9561099999999997E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="26.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="65"/>
+    </row>
+    <row r="7" spans="1:13" ht="26.25">
+      <c r="A7" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="66"/>
-    </row>
-    <row r="7" spans="1:13" ht="26.25">
-      <c r="A7" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="59"/>
-      <c r="M7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="58"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="58"/>
+      <c r="M7" s="59"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="17"/>
       <c r="B8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="B9" s="34">
+        <v>0.111292</v>
+      </c>
+      <c r="C9" s="34">
+        <v>0.103449</v>
+      </c>
+      <c r="D9" s="34">
+        <v>7.8440000000000003E-3</v>
+      </c>
+      <c r="E9" s="34">
+        <v>0.115317</v>
+      </c>
+      <c r="F9" s="34">
+        <v>0.10798099999999999</v>
+      </c>
+      <c r="G9" s="34">
+        <v>7.3369999999999998E-3</v>
+      </c>
+      <c r="H9" s="34">
+        <v>0.12066</v>
+      </c>
+      <c r="I9" s="34">
+        <v>0.11358</v>
+      </c>
+      <c r="J9" s="34">
+        <v>7.0800000000000004E-3</v>
+      </c>
+      <c r="K9" s="34">
+        <v>0.12102400000000001</v>
+      </c>
+      <c r="L9" s="34">
+        <v>0.11402900000000001</v>
+      </c>
+      <c r="M9" s="34">
+        <v>6.9965599999999998E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="26.25">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+    </row>
+    <row r="11" spans="1:13" ht="26.25">
+      <c r="A11" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-    </row>
-    <row r="11" spans="1:13" ht="26.25">
-      <c r="A11" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="59"/>
-      <c r="M11" s="60"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="58"/>
+      <c r="M11" s="59"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="17"/>
       <c r="B12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="B13" s="34">
+        <v>0.112387</v>
+      </c>
+      <c r="C13" s="34">
+        <v>0.104515</v>
+      </c>
+      <c r="D13" s="34">
+        <v>7.8729999999999998E-3</v>
+      </c>
+      <c r="E13" s="34">
+        <v>0.118108</v>
+      </c>
+      <c r="F13" s="34">
+        <v>0.110877</v>
+      </c>
+      <c r="G13" s="34">
+        <v>7.2300000000000003E-3</v>
+      </c>
+      <c r="H13" s="34">
+        <v>0.122141</v>
+      </c>
+      <c r="I13" s="34">
+        <v>0.115079</v>
+      </c>
+      <c r="J13" s="34">
+        <v>7.0600000000000003E-3</v>
+      </c>
+      <c r="K13" s="34">
+        <v>0.12202</v>
+      </c>
+      <c r="L13" s="34">
+        <v>0.114995</v>
+      </c>
+      <c r="M13" s="34">
+        <v>7.0250499999999997E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="26.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+    </row>
+    <row r="15" spans="1:13" ht="26.25">
+      <c r="A15" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="58"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.25">
-      <c r="A15" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="59"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="59"/>
-      <c r="M15" s="60"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="17"/>
       <c r="B16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
+        <v>63</v>
+      </c>
+      <c r="B17" s="34">
+        <v>0.112862</v>
+      </c>
+      <c r="C17" s="34">
+        <v>0.105045</v>
+      </c>
+      <c r="D17" s="34">
+        <v>7.8150000000000008E-3</v>
+      </c>
+      <c r="E17" s="34">
+        <v>0.120723</v>
+      </c>
+      <c r="F17" s="34">
+        <v>0.113285</v>
+      </c>
+      <c r="G17" s="34">
+        <v>7.4359999999999999E-3</v>
+      </c>
+      <c r="H17" s="34">
+        <v>0.122296</v>
+      </c>
+      <c r="I17" s="34">
+        <v>0.11512699999999999</v>
+      </c>
+      <c r="J17" s="34">
+        <v>7.1679999999999999E-3</v>
+      </c>
+      <c r="K17" s="34">
+        <v>0.122501</v>
+      </c>
+      <c r="L17" s="34">
+        <v>0.115368</v>
+      </c>
+      <c r="M17" s="34">
+        <v>7.1320000000000003E-3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -21911,111 +22145,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25">
-      <c r="A1" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
+      <c r="A1" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59.1" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="69"/>
+      <c r="A2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="76"/>
     </row>
     <row r="3" spans="1:12" ht="26.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+    </row>
+    <row r="4" spans="1:12" ht="26.25">
+      <c r="A4" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-    </row>
-    <row r="4" spans="1:12" ht="26.25">
-      <c r="A4" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -22347,79 +22581,79 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" ht="26.25">
-      <c r="A22" s="70" t="s">
+      <c r="A22" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+    </row>
+    <row r="23" spans="1:12" ht="26.25">
+      <c r="A23" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-    </row>
-    <row r="23" spans="1:12" ht="26.25">
-      <c r="A23" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L24" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -22751,79 +22985,79 @@
       <c r="L40" s="26"/>
     </row>
     <row r="41" spans="1:12" ht="26.25">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+    </row>
+    <row r="42" spans="1:12" ht="26.25">
+      <c r="A42" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-    </row>
-    <row r="42" spans="1:12" ht="26.25">
-      <c r="A42" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L43" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -23155,79 +23389,79 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" ht="26.25">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
+      <c r="L60" s="56"/>
+    </row>
+    <row r="61" spans="1:12" ht="26.25">
+      <c r="A61" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="57"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="57"/>
-      <c r="E60" s="57"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="57"/>
-      <c r="K60" s="57"/>
-      <c r="L60" s="57"/>
-    </row>
-    <row r="61" spans="1:12" ht="26.25">
-      <c r="A61" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="57"/>
+      <c r="K61" s="56"/>
+      <c r="L61" s="56"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L62" s="19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -23598,499 +23832,499 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25">
-      <c r="A1" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="76"/>
+      <c r="A1" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="83"/>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="26.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="82"/>
+    </row>
+    <row r="3" spans="1:13" s="8" customFormat="1" ht="26.25">
+      <c r="A3" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="75"/>
-    </row>
-    <row r="3" spans="1:13" s="8" customFormat="1" ht="26.25">
-      <c r="A3" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="74"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="L3" s="74"/>
-      <c r="M3" s="75"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="81"/>
+      <c r="M3" s="82"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A4" s="46"/>
       <c r="B4" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G4" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I4" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K4" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L4" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M4" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A5" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="77">
+        <v>63</v>
+      </c>
+      <c r="B5" s="49">
         <v>3.3029999999999999</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="49">
         <v>2.8420000000000001</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="49">
         <v>0.46100000000000002</v>
       </c>
-      <c r="E5" s="77">
+      <c r="E5" s="49">
         <v>3.2749999999999999</v>
       </c>
-      <c r="F5" s="77">
+      <c r="F5" s="49">
         <v>2.8079999999999998</v>
       </c>
-      <c r="G5" s="77">
+      <c r="G5" s="49">
         <v>0.46600000000000003</v>
       </c>
-      <c r="H5" s="83">
+      <c r="H5" s="55">
         <v>3.262</v>
       </c>
-      <c r="I5" s="83">
+      <c r="I5" s="55">
         <v>2.7949999999999999</v>
       </c>
-      <c r="J5" s="83">
+      <c r="J5" s="55">
         <v>0.46600000000000003</v>
       </c>
-      <c r="K5" s="83">
+      <c r="K5" s="55">
         <v>3.258</v>
       </c>
-      <c r="L5" s="83">
+      <c r="L5" s="55">
         <v>2.7909999999999999</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="55">
         <v>0.46600000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="26.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="82"/>
+    </row>
+    <row r="7" spans="1:13" s="8" customFormat="1" ht="26.25">
+      <c r="A7" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="75"/>
-    </row>
-    <row r="7" spans="1:13" s="8" customFormat="1" ht="26.25">
-      <c r="A7" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="74"/>
-      <c r="M7" s="75"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="81"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="81"/>
+      <c r="M7" s="82"/>
     </row>
     <row r="8" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A8" s="46"/>
       <c r="B8" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I8" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J8" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K8" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L8" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M8" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A9" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="77">
+        <v>63</v>
+      </c>
+      <c r="B9" s="49">
         <v>3.31</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="49">
         <v>2.8460000000000001</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="49">
         <v>0.46400000000000002</v>
       </c>
-      <c r="E9" s="77">
+      <c r="E9" s="49">
         <v>3.282</v>
       </c>
-      <c r="F9" s="77">
+      <c r="F9" s="49">
         <v>2.8130000000000002</v>
       </c>
-      <c r="G9" s="77">
+      <c r="G9" s="49">
         <v>0.46800000000000003</v>
       </c>
-      <c r="H9" s="77">
+      <c r="H9" s="49">
         <v>3.2690000000000001</v>
       </c>
-      <c r="I9" s="77">
+      <c r="I9" s="49">
         <v>2.8010000000000002</v>
       </c>
-      <c r="J9" s="77">
+      <c r="J9" s="49">
         <v>0.46800000000000003</v>
       </c>
-      <c r="K9" s="77">
+      <c r="K9" s="49">
         <v>3.2650000000000001</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="49">
         <v>2.7959999999999998</v>
       </c>
-      <c r="M9" s="77">
+      <c r="M9" s="49">
         <v>0.46800000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="45" customFormat="1" ht="26.25">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="82"/>
+    </row>
+    <row r="11" spans="1:13" s="8" customFormat="1" ht="26.25">
+      <c r="A11" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="75"/>
-    </row>
-    <row r="11" spans="1:13" s="8" customFormat="1" ht="26.25">
-      <c r="A11" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="74"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="74"/>
-      <c r="M11" s="75"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="81"/>
+      <c r="M11" s="82"/>
     </row>
     <row r="12" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A12" s="46"/>
       <c r="B12" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H12" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I12" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J12" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K12" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L12" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M12" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A13" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="77">
+        <v>63</v>
+      </c>
+      <c r="B13" s="49">
         <v>3.3340000000000001</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="49">
         <v>2.8639999999999999</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="49">
         <v>0.46899999999999997</v>
       </c>
-      <c r="E13" s="77">
+      <c r="E13" s="49">
         <v>3.3069999999999999</v>
       </c>
-      <c r="F13" s="77">
+      <c r="F13" s="49">
         <v>2.8330000000000002</v>
       </c>
-      <c r="G13" s="77">
+      <c r="G13" s="49">
         <v>0.47299999999999998</v>
       </c>
-      <c r="H13" s="77">
+      <c r="H13" s="49">
         <v>3.2949999999999999</v>
       </c>
-      <c r="I13" s="77">
+      <c r="I13" s="49">
         <v>2.8210000000000002</v>
       </c>
-      <c r="J13" s="77">
+      <c r="J13" s="49">
         <v>0.47399999999999998</v>
       </c>
-      <c r="K13" s="77">
+      <c r="K13" s="49">
         <v>3.2909999999999999</v>
       </c>
-      <c r="L13" s="77">
+      <c r="L13" s="49">
         <v>2.8170000000000002</v>
       </c>
-      <c r="M13" s="77">
+      <c r="M13" s="49">
         <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="45" customFormat="1" ht="26.25">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
+    </row>
+    <row r="15" spans="1:13" s="8" customFormat="1" ht="26.25">
+      <c r="A15" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="81"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="75"/>
-    </row>
-    <row r="15" spans="1:13" s="8" customFormat="1" ht="26.25">
-      <c r="A15" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="74"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="74"/>
-      <c r="M15" s="75"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="82"/>
     </row>
     <row r="16" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A16" s="46"/>
       <c r="B16" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G16" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H16" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I16" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J16" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K16" s="47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L16" s="47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M16" s="47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="45" customFormat="1" ht="31.5">
       <c r="A17" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="83">
+        <v>63</v>
+      </c>
+      <c r="B17" s="55">
         <v>3.472</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17" s="55">
         <v>2.9670000000000001</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="55">
         <v>0.503</v>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="55">
         <v>3.4380000000000002</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="55">
         <v>2.9329999999999998</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="55">
         <v>0.503</v>
       </c>
-      <c r="H17" s="77">
+      <c r="H17" s="49">
         <v>3.4239999999999999</v>
       </c>
-      <c r="I17" s="77">
+      <c r="I17" s="49">
         <v>2.919</v>
       </c>
-      <c r="J17" s="77">
+      <c r="J17" s="49">
         <v>0.502</v>
       </c>
-      <c r="K17" s="77">
+      <c r="K17" s="49">
         <v>3.419</v>
       </c>
-      <c r="L17" s="77">
+      <c r="L17" s="49">
         <v>2.915</v>
       </c>
-      <c r="M17" s="77">
+      <c r="M17" s="49">
         <v>0.502</v>
       </c>
     </row>
@@ -24347,41 +24581,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0A7EF3-DA59-4C57-A694-9BC7D4A5CA4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7ca3eb74-f479-4a74-8b5d-635eab9fd68d"/>
-    <ds:schemaRef ds:uri="400e00c9-3b78-4d74-b334-049d624573ce"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0A7EF3-DA59-4C57-A694-9BC7D4A5CA4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF02D46-45A8-41BE-A629-9D363DDC90B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7ca3eb74-f479-4a74-8b5d-635eab9fd68d"/>
-    <ds:schemaRef ds:uri="400e00c9-3b78-4d74-b334-049d624573ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF02D46-45A8-41BE-A629-9D363DDC90B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EB424FB-30AD-4CFA-AFBF-EA3987E44B9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EB424FB-30AD-4CFA-AFBF-EA3987E44B9B}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
